--- a/RIZE/VIETNAM/Rize Vietnam - demo pay data.xlsx
+++ b/RIZE/VIETNAM/Rize Vietnam - demo pay data.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pay data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pay data'!$A$1:$AB$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pay data'!$A$1:$I$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -93,9 +93,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -463,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -475,25 +472,6 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
-    <col hidden="1" width="4" customWidth="1" min="23" max="23"/>
-    <col hidden="1" width="4" customWidth="1" min="24" max="24"/>
-    <col hidden="1" width="4" customWidth="1" min="25" max="25"/>
-    <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="16" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1" ht="46" customHeight="1">
@@ -542,101 +520,6 @@
           <t>Night work — hours this run</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Logistics incentive</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Season agronomy incentive</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>New product launch incentive</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Referral incentive</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Variable bonus approved this run (1 = yes)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Other taxable allowance</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Additional transportation</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Unused annual-leave encashment</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Other exempt reimbursement</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Taxable non-cash benefit</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Other company benefits</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Prior-period addition</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Prior-period deduction approved</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Private insurance allowance approved</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Private health premium — employee</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Private health premium — dependants</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Salary advance recovery</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Prior-period deduction</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Other deduction</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -667,54 +550,6 @@
       <c r="I2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -745,54 +580,6 @@
       <c r="I3" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="J3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -823,54 +610,6 @@
       <c r="I4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="4" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="AA4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -901,54 +640,6 @@
       <c r="I5" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -979,57 +670,9 @@
       <c r="I6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB6"/>
+  <autoFilter ref="A1:I6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>